--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/pre LAM_HRM-2031-0140/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.73494</v>
+        <v>17.13129</v>
       </c>
       <c r="D2" t="n">
-        <v>16.66091</v>
+        <v>16.44678</v>
       </c>
       <c r="E2" t="n">
-        <v>16.65094</v>
+        <v>16.55261</v>
       </c>
       <c r="F2" t="n">
-        <v>42.33909</v>
+        <v>42.75522</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05005</v>
+        <v>0.05072</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83914</v>
+        <v>1.79634</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.94475</v>
+        <v>16.81013</v>
       </c>
       <c r="D3" t="n">
-        <v>16.62267</v>
+        <v>16.57121</v>
       </c>
       <c r="E3" t="n">
-        <v>16.47244</v>
+        <v>16.73737</v>
       </c>
       <c r="F3" t="n">
-        <v>42.95072</v>
+        <v>42.51994</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05121</v>
+        <v>0.05129</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78286</v>
+        <v>1.83778</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.7954</v>
+        <v>16.8604</v>
       </c>
       <c r="D4" t="n">
-        <v>16.88121</v>
+        <v>16.64873</v>
       </c>
       <c r="E4" t="n">
-        <v>16.80319</v>
+        <v>16.69756</v>
       </c>
       <c r="F4" t="n">
-        <v>42.42007</v>
+        <v>41.97222</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05032</v>
+        <v>0.05046</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82649</v>
+        <v>1.81265</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.61979</v>
+        <v>16.97355</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06223</v>
+        <v>15.82785</v>
       </c>
       <c r="E6" t="n">
-        <v>16.25547</v>
+        <v>16.54603</v>
       </c>
       <c r="F6" t="n">
-        <v>21.78855</v>
+        <v>21.53421</v>
       </c>
       <c r="G6" t="n">
-        <v>34.25993</v>
+        <v>34.53912</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63288</v>
+        <v>16.63827</v>
       </c>
       <c r="D7" t="n">
-        <v>16.15435</v>
+        <v>15.70437</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42976</v>
+        <v>16.09821</v>
       </c>
       <c r="F7" t="n">
-        <v>21.91536</v>
+        <v>21.49441</v>
       </c>
       <c r="G7" t="n">
-        <v>33.66295</v>
+        <v>34.16812</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.66533</v>
+        <v>16.50795</v>
       </c>
       <c r="D8" t="n">
-        <v>16.41959</v>
+        <v>15.95797</v>
       </c>
       <c r="E8" t="n">
-        <v>16.07852</v>
+        <v>16.35014</v>
       </c>
       <c r="F8" t="n">
-        <v>21.65182</v>
+        <v>21.5717</v>
       </c>
       <c r="G8" t="n">
-        <v>33.61924</v>
+        <v>34.0745</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60055</v>
+        <v>0.61531</v>
       </c>
       <c r="D10" t="n">
-        <v>1.09824</v>
+        <v>1.10912</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61651</v>
+        <v>0.59505</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11319</v>
+        <v>1.09229</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60105</v>
+        <v>0.60407</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11849</v>
+        <v>1.10508</v>
       </c>
     </row>
   </sheetData>
